--- a/lib/templates/report-mendxza.xlsx
+++ b/lib/templates/report-mendxza.xlsx
@@ -36,7 +36,7 @@
     <t>Лицензиат:</t>
   </si>
   <si>
-    <t>Латынин Максим Русланович</t>
+    <t>ИП Латынин Максим Русланович</t>
   </si>
   <si>
     <t>Лицензиар:</t>
@@ -117,7 +117,7 @@
     <t>______________/</t>
   </si>
   <si>
-    <t>Латынин М. Р.</t>
+    <t>ИП Латынин М. Р.</t>
   </si>
   <si>
     <t>Галец А. О.</t>
